--- a/data/trans_camb/P19C01-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P19C01-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 11,33</t>
+          <t>-2,83; 11,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,15; 19,31</t>
+          <t>4,23; 19,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,03; 36,53</t>
+          <t>16,85; 36,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 5,29</t>
+          <t>-8,57; 5,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 13,23</t>
+          <t>-1,36; 12,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,24; 33,92</t>
+          <t>17,89; 33,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 6,04</t>
+          <t>-4,31; 6,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 13,76</t>
+          <t>3,68; 13,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,35; 32,48</t>
+          <t>19,96; 32,95</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 30,56</t>
+          <t>-6,45; 32,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,23; 52,31</t>
+          <t>8,8; 51,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,03; 96,42</t>
+          <t>38,65; 99,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 11,99</t>
+          <t>-17,1; 11,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 29,95</t>
+          <t>-2,89; 28,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,89; 76,52</t>
+          <t>35,25; 77,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 14,18</t>
+          <t>-9,26; 14,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 32,67</t>
+          <t>7,66; 33,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41,36; 76,47</t>
+          <t>43,1; 77,6</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 7,37</t>
+          <t>-4,05; 7,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 12,89</t>
+          <t>1,88; 13,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,02; 39,71</t>
+          <t>25,5; 39,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 8,63</t>
+          <t>-3,21; 8,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 12,35</t>
+          <t>-0,05; 12,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,64; 44,37</t>
+          <t>24,29; 44,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 6,68</t>
+          <t>-2,11; 5,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 11,41</t>
+          <t>2,68; 10,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,43; 40,97</t>
+          <t>27,56; 40,28</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 24,89</t>
+          <t>-11,52; 25,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 43,12</t>
+          <t>5,51; 46,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70,58; 131,36</t>
+          <t>73,07; 132,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 24,55</t>
+          <t>-7,78; 24,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 34,7</t>
+          <t>-0,21; 35,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,94; 121,27</t>
+          <t>59,24; 124,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 20,18</t>
+          <t>-5,76; 17,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,0; 34,4</t>
+          <t>6,97; 32,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>71,4; 118,86</t>
+          <t>72,73; 116,96</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 5,53</t>
+          <t>-5,87; 5,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 16,76</t>
+          <t>4,63; 16,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,35; 36,5</t>
+          <t>24,25; 36,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 12,18</t>
+          <t>1,51; 11,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,82; 20,83</t>
+          <t>9,8; 21,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,11; 36,37</t>
+          <t>26,2; 36,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 7,28</t>
+          <t>-0,09; 7,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,9; 17,23</t>
+          <t>9,12; 17,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,07; 35,1</t>
+          <t>26,58; 34,79</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 21,04</t>
+          <t>-17,31; 21,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,42; 62,9</t>
+          <t>13,58; 60,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73,64; 134,85</t>
+          <t>72,25; 136,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,69; 42,64</t>
+          <t>4,38; 40,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,14; 73,3</t>
+          <t>27,78; 72,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>75,39; 127,49</t>
+          <t>75,44; 128,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 25,16</t>
+          <t>-0,38; 26,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,77; 58,77</t>
+          <t>27,24; 58,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>82,51; 125,24</t>
+          <t>80,96; 122,24</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 6,77</t>
+          <t>-5,29; 6,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,35; 22,23</t>
+          <t>9,13; 21,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 36,86</t>
+          <t>-9,07; 36,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 11,18</t>
+          <t>-1,08; 10,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,9; 20,71</t>
+          <t>8,86; 20,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,66; 35,27</t>
+          <t>19,83; 35,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 7,35</t>
+          <t>-1,52; 6,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,95; 20,04</t>
+          <t>10,85; 19,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 33,66</t>
+          <t>2,09; 33,75</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,2; 30,6</t>
+          <t>-17,84; 28,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31,16; 98,52</t>
+          <t>30,88; 95,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,37; 151,71</t>
+          <t>-27,62; 150,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 42,2</t>
+          <t>-3,15; 41,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>28,06; 80,23</t>
+          <t>27,18; 81,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,43; 138,02</t>
+          <t>63,87; 139,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 29,55</t>
+          <t>-5,04; 28,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>36,27; 79,4</t>
+          <t>36,6; 80,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,36; 126,77</t>
+          <t>11,22; 127,71</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 6,05</t>
+          <t>-8,13; 6,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,19; 17,04</t>
+          <t>2,23; 17,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18,21; 31,96</t>
+          <t>17,54; 31,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 13,61</t>
+          <t>-0,25; 13,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,03; 24,73</t>
+          <t>11,55; 25,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,98; 40,03</t>
+          <t>29,05; 40,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 7,53</t>
+          <t>-2,1; 7,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,15; 18,44</t>
+          <t>8,56; 19,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25,66; 34,54</t>
+          <t>25,94; 34,56</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-26,16; 28,04</t>
+          <t>-26,26; 30,19</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6,49; 74,63</t>
+          <t>7,36; 77,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59,03; 148,76</t>
+          <t>56,93; 147,16</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 74,08</t>
+          <t>-2,39; 71,57</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>43,07; 134,26</t>
+          <t>46,49; 141,01</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>112,5; 227,62</t>
+          <t>111,33; 225,6</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 35,93</t>
+          <t>-7,77; 36,29</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>30,67; 89,78</t>
+          <t>31,72; 89,06</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>93,85; 166,96</t>
+          <t>97,43; 169,32</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 1,72</t>
+          <t>-12,34; 3,04</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4,01; 21,71</t>
+          <t>5,29; 22,81</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19,74; 34,4</t>
+          <t>19,88; 34,05</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 9,29</t>
+          <t>-4,56; 9,22</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,06; 22,34</t>
+          <t>7,14; 21,6</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 33,59</t>
+          <t>-8,18; 33,73</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 4,01</t>
+          <t>-5,88; 4,09</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>8,12; 19,99</t>
+          <t>8,53; 19,54</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 31,49</t>
+          <t>-1,48; 31,35</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-47,32; 10,82</t>
+          <t>-47,92; 18,71</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15,91; 121,88</t>
+          <t>19,73; 130,49</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>72,99; 206,04</t>
+          <t>71,67; 198,3</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 54,77</t>
+          <t>-19,33; 54,59</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>28,86; 131,51</t>
+          <t>29,13; 129,25</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 176,21</t>
+          <t>-34,88; 178,8</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-24,9; 21,72</t>
+          <t>-25,58; 20,76</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>33,39; 110,51</t>
+          <t>35,01; 106,47</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 158,39</t>
+          <t>-2,32; 157,63</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 3,32</t>
+          <t>-13,74; 3,91</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,19; 21,82</t>
+          <t>2,47; 20,85</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14,52; 30,91</t>
+          <t>14,82; 31,75</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 10,93</t>
+          <t>-4,5; 9,41</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,21; 25,2</t>
+          <t>7,86; 25,4</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,22; 30,87</t>
+          <t>18,02; 31,16</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 6,06</t>
+          <t>-5,07; 6,12</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>8,13; 21,82</t>
+          <t>7,92; 20,99</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>19,81; 29,42</t>
+          <t>19,17; 29,53</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-60,77; 23,31</t>
+          <t>-57,88; 32,54</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>8,31; 160,54</t>
+          <t>9,3; 156,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>56,84; 259,66</t>
+          <t>62,35; 258,8</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-18,41; 92,63</t>
+          <t>-21,2; 75,42</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>34,01; 202,67</t>
+          <t>36,69; 203,24</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>80,5; 266,05</t>
+          <t>81,54; 261,94</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-25,64; 45,05</t>
+          <t>-25,79; 45,09</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>39,81; 162,66</t>
+          <t>39,65; 154,93</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>99,47; 219,84</t>
+          <t>91,81; 224,5</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 2,03</t>
+          <t>-2,77; 2,36</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>8,32; 13,67</t>
+          <t>8,22; 13,7</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>11,73; 28,69</t>
+          <t>11,13; 28,62</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,51</t>
+          <t>0,27; 5,26</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>9,32; 14,7</t>
+          <t>9,48; 14,79</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>13,16; 29,07</t>
+          <t>12,99; 28,78</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 3,1</t>
+          <t>-0,47; 3,17</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>9,49; 13,31</t>
+          <t>9,71; 13,25</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>16,89; 27,91</t>
+          <t>16,28; 27,45</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 7,14</t>
+          <t>-8,95; 8,31</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>26,74; 47,87</t>
+          <t>26,39; 48,5</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>38,95; 98,94</t>
+          <t>34,43; 97,93</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1,0; 18,41</t>
+          <t>0,93; 17,42</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>28,64; 48,73</t>
+          <t>28,62; 48,68</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>42,6; 94,76</t>
+          <t>42,59; 93,87</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 10,51</t>
+          <t>-1,49; 10,48</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>29,96; 44,95</t>
+          <t>30,89; 44,55</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>56,86; 92,73</t>
+          <t>53,66; 91,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C01-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P19C01-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27,3</t>
+          <t>25,16</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,99</t>
+          <t>24,98</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26,25</t>
+          <t>24,83</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 11,77</t>
+          <t>-2,51; 11,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 19,52</t>
+          <t>3,93; 18,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,85; 36,96</t>
+          <t>15,1; 34,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 5,37</t>
+          <t>-8,82; 5,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 12,32</t>
+          <t>-1,24; 12,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,89; 33,75</t>
+          <t>15,42; 32,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 6,07</t>
+          <t>-4,11; 6,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,68; 13,76</t>
+          <t>3,35; 13,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,96; 32,95</t>
+          <t>17,19; 30,56</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>55,86%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 32,49</t>
+          <t>-5,79; 31,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,8; 51,43</t>
+          <t>8,43; 51,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,65; 99,12</t>
+          <t>34,29; 93,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 11,99</t>
+          <t>-17,29; 12,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 28,37</t>
+          <t>-2,51; 28,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,25; 77,15</t>
+          <t>30,99; 74,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 14,34</t>
+          <t>-8,88; 14,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,66; 33,12</t>
+          <t>7,23; 33,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43,1; 77,6</t>
+          <t>37,24; 73,72</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32,75</t>
+          <t>32,85</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,01</t>
+          <t>26,4</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>32,72</t>
+          <t>29,69</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 7,83</t>
+          <t>-4,14; 7,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 13,86</t>
+          <t>1,26; 13,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,5; 39,6</t>
+          <t>25,66; 40,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 8,51</t>
+          <t>-3,81; 8,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 12,41</t>
+          <t>0,08; 12,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,29; 44,53</t>
+          <t>19,89; 32,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 5,99</t>
+          <t>-2,4; 6,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 10,97</t>
+          <t>2,85; 11,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,56; 40,28</t>
+          <t>25,02; 34,51</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>100,21%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>83,44%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 25,4</t>
+          <t>-11,35; 25,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 46,28</t>
+          <t>3,65; 43,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,07; 132,64</t>
+          <t>72,35; 137,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 24,21</t>
+          <t>-9,22; 24,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 35,13</t>
+          <t>0,57; 33,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,24; 124,23</t>
+          <t>47,39; 90,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 17,68</t>
+          <t>-6,16; 18,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,97; 32,6</t>
+          <t>7,65; 34,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>72,73; 116,96</t>
+          <t>67,02; 102,25</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30,51</t>
+          <t>29,91</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,53</t>
+          <t>31,72</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30,97</t>
+          <t>30,76</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 5,65</t>
+          <t>-5,78; 6,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,63; 16,34</t>
+          <t>5,18; 16,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,25; 36,9</t>
+          <t>23,38; 35,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 11,57</t>
+          <t>0,8; 11,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,8; 21,07</t>
+          <t>9,27; 21,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,2; 36,3</t>
+          <t>26,62; 36,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 7,72</t>
+          <t>-0,14; 7,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,12; 17,09</t>
+          <t>9,01; 16,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26,58; 34,79</t>
+          <t>26,75; 34,6</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101,7%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>100,3%</t>
+          <t>100,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>100,59%</t>
+          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,31; 21,13</t>
+          <t>-17,33; 22,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,58; 60,23</t>
+          <t>15,29; 62,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72,25; 136,37</t>
+          <t>70,14; 132,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,38; 40,8</t>
+          <t>2,19; 40,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,78; 72,41</t>
+          <t>27,19; 76,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>75,44; 128,51</t>
+          <t>76,45; 128,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 26,67</t>
+          <t>-0,47; 26,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27,24; 58,81</t>
+          <t>27,56; 58,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>80,96; 122,24</t>
+          <t>80,87; 121,44</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17,48</t>
+          <t>33,51</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,65</t>
+          <t>33,01</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>22,7</t>
+          <t>33,24</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 6,38</t>
+          <t>-5,63; 5,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,13; 21,99</t>
+          <t>9,61; 22,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 36,19</t>
+          <t>28,37; 39,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 10,76</t>
+          <t>-1,84; 10,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,86; 20,98</t>
+          <t>9,23; 21,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,83; 35,3</t>
+          <t>27,88; 38,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 6,91</t>
+          <t>-1,84; 6,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,85; 19,67</t>
+          <t>11,29; 19,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,09; 33,75</t>
+          <t>29,14; 37,03</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>129,86%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>102,12%</t>
+          <t>113,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>120,92%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,84; 28,45</t>
+          <t>-19,13; 25,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30,88; 95,54</t>
+          <t>32,36; 102,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,62; 150,54</t>
+          <t>97,98; 183,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 41,3</t>
+          <t>-5,47; 41,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,18; 81,57</t>
+          <t>26,93; 81,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,87; 139,3</t>
+          <t>84,57; 152,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 28,31</t>
+          <t>-5,98; 27,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>36,6; 80,03</t>
+          <t>36,64; 77,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,22; 127,71</t>
+          <t>94,5; 148,28</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25,21</t>
+          <t>25,24</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,89</t>
+          <t>34,83</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>30,24</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 6,92</t>
+          <t>-7,86; 6,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,23; 17,05</t>
+          <t>2,28; 16,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,54; 31,68</t>
+          <t>17,96; 31,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 13,06</t>
+          <t>0,23; 13,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,55; 25,52</t>
+          <t>11,08; 25,39</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,05; 40,51</t>
+          <t>29,13; 40,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 7,56</t>
+          <t>-2,1; 7,97</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,56; 19,08</t>
+          <t>9,06; 19,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25,94; 34,56</t>
+          <t>25,87; 34,7</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>163,22%</t>
+          <t>162,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>127,7%</t>
+          <t>127,77%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-26,26; 30,19</t>
+          <t>-27,19; 27,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7,36; 77,7</t>
+          <t>6,41; 77,16</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56,93; 147,16</t>
+          <t>57,03; 144,42</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 71,57</t>
+          <t>0,98; 74,81</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>46,49; 141,01</t>
+          <t>45,63; 145,58</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>111,33; 225,6</t>
+          <t>111,21; 224,41</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 36,29</t>
+          <t>-8,23; 38,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>31,72; 89,06</t>
+          <t>34,29; 92,25</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>97,43; 169,32</t>
+          <t>94,54; 168,7</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27,92</t>
+          <t>28,58</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,02</t>
+          <t>32,46</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>19,1</t>
+          <t>30,62</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 3,04</t>
+          <t>-12,04; 2,98</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5,29; 22,81</t>
+          <t>6,05; 22,75</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19,88; 34,05</t>
+          <t>21,07; 35,48</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 9,22</t>
+          <t>-4,04; 9,55</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,14; 21,6</t>
+          <t>6,73; 22,07</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 33,73</t>
+          <t>26,34; 38,04</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 4,09</t>
+          <t>-5,58; 4,16</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>8,53; 19,54</t>
+          <t>8,89; 20,25</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 31,35</t>
+          <t>26,15; 35,03</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>128,7%</t>
+          <t>131,72%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>160,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>146,21%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-47,92; 18,71</t>
+          <t>-46,71; 16,69</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>19,73; 130,49</t>
+          <t>25,1; 134,45</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>71,67; 198,3</t>
+          <t>79,73; 213,75</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-19,33; 54,59</t>
+          <t>-18,22; 57,81</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>29,13; 129,25</t>
+          <t>27,39; 130,29</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-34,88; 178,8</t>
+          <t>105,08; 234,18</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-25,58; 20,76</t>
+          <t>-24,07; 24,24</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>35,01; 106,47</t>
+          <t>36,33; 112,97</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 157,63</t>
+          <t>105,94; 199,05</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23,78</t>
+          <t>24,22</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,03</t>
+          <t>25,93</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>24,57</t>
+          <t>25,28</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 3,91</t>
+          <t>-12,2; 3,38</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,47; 20,85</t>
+          <t>1,97; 20,97</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14,82; 31,75</t>
+          <t>15,65; 31,89</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 9,41</t>
+          <t>-3,26; 10,85</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,86; 25,4</t>
+          <t>7,23; 24,38</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,02; 31,16</t>
+          <t>19,31; 32,31</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 6,12</t>
+          <t>-5,0; 6,3</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>7,92; 20,99</t>
+          <t>8,06; 21,05</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>19,17; 29,53</t>
+          <t>19,88; 30,48</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>133,31%</t>
+          <t>135,78%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>153,93%</t>
+          <t>159,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>145,72%</t>
+          <t>149,97%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-57,88; 32,54</t>
+          <t>-55,56; 28,67</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>9,3; 156,18</t>
+          <t>7,17; 155,33</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>62,35; 258,8</t>
+          <t>62,19; 261,68</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-21,2; 75,42</t>
+          <t>-16,36; 92,53</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>36,69; 203,24</t>
+          <t>36,36; 198,23</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>81,54; 261,94</t>
+          <t>88,89; 274,53</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 45,09</t>
+          <t>-25,29; 48,07</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>39,65; 154,93</t>
+          <t>39,66; 155,9</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>91,81; 224,5</t>
+          <t>94,49; 234,78</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>23,58</t>
+          <t>27,25</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,43</t>
+          <t>27,74</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>24,0</t>
+          <t>27,49</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 2,36</t>
+          <t>-3,28; 1,98</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>8,22; 13,7</t>
+          <t>8,47; 13,83</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>11,13; 28,62</t>
+          <t>24,49; 30,08</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,27; 5,26</t>
+          <t>0,06; 5,53</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>9,48; 14,79</t>
+          <t>9,36; 14,53</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>12,99; 28,78</t>
+          <t>25,5; 29,99</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 3,17</t>
+          <t>-0,64; 3,03</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>9,71; 13,25</t>
+          <t>9,64; 13,39</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>16,28; 27,45</t>
+          <t>25,5; 29,12</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 8,31</t>
+          <t>-10,53; 7,08</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>26,39; 48,5</t>
+          <t>26,93; 48,48</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>34,43; 97,93</t>
+          <t>77,87; 106,62</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>0,93; 17,42</t>
+          <t>0,19; 18,34</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>28,62; 48,68</t>
+          <t>28,56; 48,14</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>42,59; 93,87</t>
+          <t>77,28; 100,24</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 10,48</t>
+          <t>-2,07; 10,29</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>30,89; 44,55</t>
+          <t>30,26; 44,75</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>53,66; 91,33</t>
+          <t>80,87; 98,57</t>
         </is>
       </c>
     </row>
